--- a/SuppXLS/Scen_B_TRA_Emissions.xlsx
+++ b/SuppXLS/Scen_B_TRA_Emissions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rbsul\Documents\GitHub\times-ireland-model-VA\SuppXLS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda_models\TIM 2100\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7976BD31-61F4-44FD-9224-C95A90E46F64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F94C4CA-613E-4AFE-9D4C-DE3E38872DC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="16" r:id="rId1"/>
@@ -160,7 +160,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="102">
   <si>
     <t>Pset_CI</t>
   </si>
@@ -467,16 +467,25 @@
     <t>Scenario</t>
   </si>
   <si>
-    <t>T-A*INT*,T-NAV*</t>
-  </si>
-  <si>
     <t>Pset_PN</t>
   </si>
   <si>
-    <t>-T-A*INT*,-T-NAV*</t>
-  </si>
-  <si>
     <t>TRACO2INT</t>
+  </si>
+  <si>
+    <t>T-*AVI*INT*,T-NAV*</t>
+  </si>
+  <si>
+    <t>-T-*AVI*INT*,-T-NAV*</t>
+  </si>
+  <si>
+    <t>https://www.nature.com/articles/s41558-022-01485-4</t>
+  </si>
+  <si>
+    <t>TRABJK</t>
+  </si>
+  <si>
+    <t>*AVI*</t>
   </si>
 </sst>
 </file>
@@ -486,7 +495,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -594,6 +603,13 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B0F0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -722,7 +738,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -790,6 +806,12 @@
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -799,9 +821,6 @@
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1197,6 +1216,121 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>510540</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>160020</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>16510</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>145415</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5B350536-BE4F-6D3E-6FD7-F8D83AAAD878}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2423160" y="2636520"/>
+          <a:ext cx="5731510" cy="5288915"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>182880</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>99060</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>213360</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="Rectangle 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{24BE8FDE-F446-72E8-8AC6-2203D15CEDB5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4290060" y="7330440"/>
+          <a:ext cx="472440" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IE" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
@@ -1486,20 +1620,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8055F6A0-D2D6-4192-A4C2-30BCAA062016}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:Z99"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="4" width="21.7265625" customWidth="1"/>
-    <col min="5" max="6" width="14.1796875" customWidth="1"/>
-    <col min="7" max="7" width="12.1796875" customWidth="1"/>
-    <col min="8" max="10" width="8.1796875" customWidth="1"/>
-    <col min="11" max="11" width="9.7265625" customWidth="1"/>
-    <col min="12" max="12" width="8.1796875" customWidth="1"/>
+    <col min="1" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="6" width="14.28515625" customWidth="1"/>
+    <col min="7" max="7" width="12.28515625" customWidth="1"/>
+    <col min="8" max="10" width="8.28515625" customWidth="1"/>
+    <col min="11" max="11" width="9.7109375" customWidth="1"/>
+    <col min="12" max="12" width="8.28515625" customWidth="1"/>
     <col min="13" max="13" width="10" customWidth="1"/>
-    <col min="14" max="14" width="11.453125" customWidth="1"/>
-    <col min="15" max="15" width="13.453125" customWidth="1"/>
+    <col min="14" max="14" width="11.42578125" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" s="13"/>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
@@ -1527,7 +1661,7 @@
       <c r="Y1" s="14"/>
       <c r="Z1" s="14"/>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="13"/>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
@@ -1555,7 +1689,7 @@
       <c r="Y2" s="14"/>
       <c r="Z2" s="14"/>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" s="13"/>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -1583,7 +1717,7 @@
       <c r="Y3" s="14"/>
       <c r="Z3" s="14"/>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -1611,7 +1745,7 @@
       <c r="Y4" s="14"/>
       <c r="Z4" s="14"/>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="13"/>
       <c r="B5" s="13"/>
       <c r="C5" s="13"/>
@@ -1639,7 +1773,7 @@
       <c r="Y5" s="14"/>
       <c r="Z5" s="14"/>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="13"/>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -1667,7 +1801,7 @@
       <c r="Y6" s="14"/>
       <c r="Z6" s="14"/>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" s="13"/>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -1695,7 +1829,7 @@
       <c r="Y7" s="14"/>
       <c r="Z7" s="14"/>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" s="13"/>
       <c r="B8" s="13"/>
       <c r="C8" s="13"/>
@@ -1723,7 +1857,7 @@
       <c r="Y8" s="14"/>
       <c r="Z8" s="14"/>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" s="13"/>
       <c r="B9" s="13"/>
       <c r="C9" s="13"/>
@@ -1751,7 +1885,7 @@
       <c r="Y9" s="14"/>
       <c r="Z9" s="14"/>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" s="13"/>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
@@ -1779,7 +1913,7 @@
       <c r="Y10" s="14"/>
       <c r="Z10" s="14"/>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" s="13"/>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -1807,7 +1941,7 @@
       <c r="Y11" s="14"/>
       <c r="Z11" s="14"/>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" s="13"/>
       <c r="B12" s="13"/>
       <c r="C12" s="13"/>
@@ -1835,7 +1969,7 @@
       <c r="Y12" s="14"/>
       <c r="Z12" s="14"/>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" s="13"/>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -1863,7 +1997,7 @@
       <c r="Y13" s="14"/>
       <c r="Z13" s="14"/>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" s="13"/>
       <c r="B14" s="13"/>
       <c r="C14" s="13"/>
@@ -1891,7 +2025,7 @@
       <c r="Y14" s="14"/>
       <c r="Z14" s="14"/>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" s="13"/>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -1919,13 +2053,13 @@
       <c r="Y15" s="14"/>
       <c r="Z15" s="14"/>
     </row>
-    <row r="16" spans="1:26" ht="102.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="29" t="s">
+    <row r="16" spans="1:26" ht="102.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="33" t="s">
         <v>78</v>
       </c>
-      <c r="B16" s="29"/>
-      <c r="C16" s="29"/>
-      <c r="D16" s="29"/>
+      <c r="B16" s="33"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
       <c r="E16" s="15"/>
       <c r="F16" s="15"/>
       <c r="G16" s="16"/>
@@ -1949,7 +2083,7 @@
       <c r="Y16" s="14"/>
       <c r="Z16" s="14"/>
     </row>
-    <row r="17" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="17"/>
       <c r="B17" s="17"/>
       <c r="C17" s="17"/>
@@ -1977,7 +2111,7 @@
       <c r="Y17" s="14"/>
       <c r="Z17" s="14"/>
     </row>
-    <row r="18" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="17"/>
       <c r="B18" s="17"/>
       <c r="C18" s="17"/>
@@ -2005,15 +2139,15 @@
       <c r="Y18" s="14"/>
       <c r="Z18" s="14"/>
     </row>
-    <row r="19" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="B19" s="28" t="s">
+      <c r="B19" s="32" t="s">
         <v>94</v>
       </c>
-      <c r="C19" s="28"/>
-      <c r="D19" s="28"/>
+      <c r="C19" s="32"/>
+      <c r="D19" s="32"/>
       <c r="E19" s="21"/>
       <c r="F19" s="21"/>
       <c r="G19" s="22"/>
@@ -2037,15 +2171,15 @@
       <c r="Y19" s="14"/>
       <c r="Z19" s="14"/>
     </row>
-    <row r="20" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="B20" s="28" t="s">
+      <c r="B20" s="32" t="s">
         <v>93</v>
       </c>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
+      <c r="C20" s="32"/>
+      <c r="D20" s="32"/>
       <c r="E20" s="21"/>
       <c r="F20" s="21"/>
       <c r="G20" s="22"/>
@@ -2069,7 +2203,7 @@
       <c r="Y20" s="14"/>
       <c r="Z20" s="14"/>
     </row>
-    <row r="21" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="20" t="s">
         <v>81</v>
       </c>
@@ -2101,7 +2235,7 @@
       <c r="Y21" s="14"/>
       <c r="Z21" s="14"/>
     </row>
-    <row r="22" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="20"/>
       <c r="B22" s="23"/>
       <c r="C22" s="23"/>
@@ -2129,15 +2263,15 @@
       <c r="Y22" s="14"/>
       <c r="Z22" s="14"/>
     </row>
-    <row r="23" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="B23" s="28" t="s">
+      <c r="B23" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28"/>
+      <c r="C23" s="32"/>
+      <c r="D23" s="32"/>
       <c r="E23" s="14"/>
       <c r="F23" s="14"/>
       <c r="G23" s="14"/>
@@ -2161,11 +2295,11 @@
       <c r="Y23" s="14"/>
       <c r="Z23" s="14"/>
     </row>
-    <row r="24" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="20"/>
-      <c r="B24" s="28"/>
-      <c r="C24" s="28"/>
-      <c r="D24" s="28"/>
+      <c r="B24" s="32"/>
+      <c r="C24" s="32"/>
+      <c r="D24" s="32"/>
       <c r="E24" s="14"/>
       <c r="F24" s="14"/>
       <c r="G24" s="14"/>
@@ -2189,7 +2323,7 @@
       <c r="Y24" s="14"/>
       <c r="Z24" s="14"/>
     </row>
-    <row r="25" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="20"/>
       <c r="B25" s="23"/>
       <c r="C25" s="23"/>
@@ -2217,15 +2351,15 @@
       <c r="Y25" s="14"/>
       <c r="Z25" s="14"/>
     </row>
-    <row r="26" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="B26" s="28" t="s">
+      <c r="B26" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="C26" s="28"/>
-      <c r="D26" s="28"/>
+      <c r="C26" s="32"/>
+      <c r="D26" s="32"/>
       <c r="E26" s="14"/>
       <c r="F26" s="14"/>
       <c r="G26" s="14"/>
@@ -2249,13 +2383,13 @@
       <c r="Y26" s="14"/>
       <c r="Z26" s="14"/>
     </row>
-    <row r="27" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="20"/>
-      <c r="B27" s="28" t="s">
+      <c r="B27" s="32" t="s">
         <v>91</v>
       </c>
-      <c r="C27" s="28"/>
-      <c r="D27" s="28"/>
+      <c r="C27" s="32"/>
+      <c r="D27" s="32"/>
       <c r="E27" s="14"/>
       <c r="F27" s="14"/>
       <c r="G27" s="14"/>
@@ -2279,7 +2413,7 @@
       <c r="Y27" s="14"/>
       <c r="Z27" s="14"/>
     </row>
-    <row r="28" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="20"/>
       <c r="B28" s="23"/>
       <c r="C28" s="23"/>
@@ -2307,7 +2441,7 @@
       <c r="Y28" s="14"/>
       <c r="Z28" s="14"/>
     </row>
-    <row r="29" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="20" t="s">
         <v>84</v>
       </c>
@@ -2339,15 +2473,15 @@
       <c r="Y29" s="14"/>
       <c r="Z29" s="14"/>
     </row>
-    <row r="30" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="B30" s="30" t="s">
+      <c r="B30" s="34" t="s">
         <v>86</v>
       </c>
-      <c r="C30" s="28"/>
-      <c r="D30" s="28"/>
+      <c r="C30" s="32"/>
+      <c r="D30" s="32"/>
       <c r="E30" s="25"/>
       <c r="F30" s="25"/>
       <c r="G30" s="14"/>
@@ -2371,15 +2505,15 @@
       <c r="Y30" s="14"/>
       <c r="Z30" s="14"/>
     </row>
-    <row r="31" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="B31" s="28" t="s">
+      <c r="B31" s="32" t="s">
         <v>88</v>
       </c>
-      <c r="C31" s="28"/>
-      <c r="D31" s="28"/>
+      <c r="C31" s="32"/>
+      <c r="D31" s="32"/>
       <c r="E31" s="25"/>
       <c r="F31" s="25"/>
       <c r="G31" s="14"/>
@@ -2403,7 +2537,7 @@
       <c r="Y31" s="14"/>
       <c r="Z31" s="14"/>
     </row>
-    <row r="32" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="26"/>
       <c r="B32" s="27" t="s">
         <v>89</v>
@@ -2433,7 +2567,7 @@
       <c r="Y32" s="14"/>
       <c r="Z32" s="14"/>
     </row>
-    <row r="33" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A33" s="13"/>
       <c r="B33" s="13"/>
       <c r="C33" s="13"/>
@@ -2461,7 +2595,7 @@
       <c r="Y33" s="14"/>
       <c r="Z33" s="14"/>
     </row>
-    <row r="34" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A34" s="13"/>
       <c r="B34" s="13"/>
       <c r="C34" s="13"/>
@@ -2489,7 +2623,7 @@
       <c r="Y34" s="14"/>
       <c r="Z34" s="14"/>
     </row>
-    <row r="35" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A35" s="13"/>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -2517,7 +2651,7 @@
       <c r="Y35" s="14"/>
       <c r="Z35" s="14"/>
     </row>
-    <row r="36" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A36" s="13"/>
       <c r="B36" s="13"/>
       <c r="C36" s="13"/>
@@ -2545,7 +2679,7 @@
       <c r="Y36" s="14"/>
       <c r="Z36" s="14"/>
     </row>
-    <row r="37" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A37" s="13"/>
       <c r="B37" s="13"/>
       <c r="C37" s="13"/>
@@ -2573,7 +2707,7 @@
       <c r="Y37" s="14"/>
       <c r="Z37" s="14"/>
     </row>
-    <row r="38" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A38" s="13"/>
       <c r="B38" s="13"/>
       <c r="C38" s="13"/>
@@ -2601,7 +2735,7 @@
       <c r="Y38" s="14"/>
       <c r="Z38" s="14"/>
     </row>
-    <row r="39" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A39" s="13"/>
       <c r="B39" s="13"/>
       <c r="C39" s="13"/>
@@ -2629,7 +2763,7 @@
       <c r="Y39" s="14"/>
       <c r="Z39" s="14"/>
     </row>
-    <row r="40" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A40" s="13"/>
       <c r="B40" s="13"/>
       <c r="C40" s="13"/>
@@ -2657,7 +2791,7 @@
       <c r="Y40" s="14"/>
       <c r="Z40" s="14"/>
     </row>
-    <row r="41" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A41" s="13"/>
       <c r="B41" s="13"/>
       <c r="C41" s="13"/>
@@ -2685,7 +2819,7 @@
       <c r="Y41" s="14"/>
       <c r="Z41" s="14"/>
     </row>
-    <row r="42" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A42" s="13"/>
       <c r="B42" s="13"/>
       <c r="C42" s="13"/>
@@ -2713,7 +2847,7 @@
       <c r="Y42" s="14"/>
       <c r="Z42" s="14"/>
     </row>
-    <row r="43" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A43" s="14"/>
       <c r="B43" s="14"/>
       <c r="C43" s="14"/>
@@ -2741,7 +2875,7 @@
       <c r="Y43" s="14"/>
       <c r="Z43" s="14"/>
     </row>
-    <row r="44" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A44" s="14"/>
       <c r="B44" s="14"/>
       <c r="C44" s="14"/>
@@ -2769,7 +2903,7 @@
       <c r="Y44" s="14"/>
       <c r="Z44" s="14"/>
     </row>
-    <row r="45" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A45" s="14"/>
       <c r="B45" s="14"/>
       <c r="C45" s="14"/>
@@ -2797,7 +2931,7 @@
       <c r="Y45" s="14"/>
       <c r="Z45" s="14"/>
     </row>
-    <row r="46" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A46" s="14"/>
       <c r="B46" s="14"/>
       <c r="C46" s="14"/>
@@ -2825,7 +2959,7 @@
       <c r="Y46" s="14"/>
       <c r="Z46" s="14"/>
     </row>
-    <row r="47" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A47" s="14"/>
       <c r="B47" s="14"/>
       <c r="C47" s="14"/>
@@ -2853,7 +2987,7 @@
       <c r="Y47" s="14"/>
       <c r="Z47" s="14"/>
     </row>
-    <row r="48" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A48" s="14"/>
       <c r="B48" s="14"/>
       <c r="C48" s="14"/>
@@ -2881,7 +3015,7 @@
       <c r="Y48" s="14"/>
       <c r="Z48" s="14"/>
     </row>
-    <row r="49" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A49" s="14"/>
       <c r="B49" s="14"/>
       <c r="C49" s="14"/>
@@ -2909,7 +3043,7 @@
       <c r="Y49" s="14"/>
       <c r="Z49" s="14"/>
     </row>
-    <row r="50" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A50" s="14"/>
       <c r="B50" s="14"/>
       <c r="C50" s="14"/>
@@ -2937,7 +3071,7 @@
       <c r="Y50" s="14"/>
       <c r="Z50" s="14"/>
     </row>
-    <row r="51" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A51" s="14"/>
       <c r="B51" s="14"/>
       <c r="C51" s="14"/>
@@ -2965,7 +3099,7 @@
       <c r="Y51" s="14"/>
       <c r="Z51" s="14"/>
     </row>
-    <row r="52" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A52" s="14"/>
       <c r="B52" s="14"/>
       <c r="C52" s="14"/>
@@ -2993,7 +3127,7 @@
       <c r="Y52" s="14"/>
       <c r="Z52" s="14"/>
     </row>
-    <row r="53" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A53" s="14"/>
       <c r="B53" s="14"/>
       <c r="C53" s="14"/>
@@ -3021,7 +3155,7 @@
       <c r="Y53" s="14"/>
       <c r="Z53" s="14"/>
     </row>
-    <row r="54" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A54" s="14"/>
       <c r="B54" s="14"/>
       <c r="C54" s="14"/>
@@ -3049,7 +3183,7 @@
       <c r="Y54" s="14"/>
       <c r="Z54" s="14"/>
     </row>
-    <row r="55" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A55" s="14"/>
       <c r="B55" s="14"/>
       <c r="C55" s="14"/>
@@ -3077,7 +3211,7 @@
       <c r="Y55" s="14"/>
       <c r="Z55" s="14"/>
     </row>
-    <row r="56" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A56" s="14"/>
       <c r="B56" s="14"/>
       <c r="C56" s="14"/>
@@ -3105,7 +3239,7 @@
       <c r="Y56" s="14"/>
       <c r="Z56" s="14"/>
     </row>
-    <row r="57" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A57" s="14"/>
       <c r="B57" s="14"/>
       <c r="C57" s="14"/>
@@ -3133,7 +3267,7 @@
       <c r="Y57" s="14"/>
       <c r="Z57" s="14"/>
     </row>
-    <row r="58" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A58" s="14"/>
       <c r="B58" s="14"/>
       <c r="C58" s="14"/>
@@ -3161,7 +3295,7 @@
       <c r="Y58" s="14"/>
       <c r="Z58" s="14"/>
     </row>
-    <row r="59" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A59" s="14"/>
       <c r="B59" s="14"/>
       <c r="C59" s="14"/>
@@ -3189,7 +3323,7 @@
       <c r="Y59" s="14"/>
       <c r="Z59" s="14"/>
     </row>
-    <row r="60" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A60" s="14"/>
       <c r="B60" s="14"/>
       <c r="C60" s="14"/>
@@ -3217,7 +3351,7 @@
       <c r="Y60" s="14"/>
       <c r="Z60" s="14"/>
     </row>
-    <row r="61" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A61" s="14"/>
       <c r="B61" s="14"/>
       <c r="C61" s="14"/>
@@ -3245,7 +3379,7 @@
       <c r="Y61" s="14"/>
       <c r="Z61" s="14"/>
     </row>
-    <row r="62" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A62" s="14"/>
       <c r="B62" s="14"/>
       <c r="C62" s="14"/>
@@ -3273,7 +3407,7 @@
       <c r="Y62" s="14"/>
       <c r="Z62" s="14"/>
     </row>
-    <row r="63" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A63" s="14"/>
       <c r="B63" s="14"/>
       <c r="C63" s="14"/>
@@ -3301,7 +3435,7 @@
       <c r="Y63" s="14"/>
       <c r="Z63" s="14"/>
     </row>
-    <row r="64" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A64" s="14"/>
       <c r="B64" s="14"/>
       <c r="C64" s="14"/>
@@ -3329,7 +3463,7 @@
       <c r="Y64" s="14"/>
       <c r="Z64" s="14"/>
     </row>
-    <row r="65" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A65" s="14"/>
       <c r="B65" s="14"/>
       <c r="C65" s="14"/>
@@ -3357,7 +3491,7 @@
       <c r="Y65" s="14"/>
       <c r="Z65" s="14"/>
     </row>
-    <row r="66" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A66" s="14"/>
       <c r="B66" s="14"/>
       <c r="C66" s="14"/>
@@ -3385,7 +3519,7 @@
       <c r="Y66" s="14"/>
       <c r="Z66" s="14"/>
     </row>
-    <row r="67" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A67" s="14"/>
       <c r="B67" s="14"/>
       <c r="C67" s="14"/>
@@ -3413,7 +3547,7 @@
       <c r="Y67" s="14"/>
       <c r="Z67" s="14"/>
     </row>
-    <row r="68" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A68" s="14"/>
       <c r="B68" s="14"/>
       <c r="C68" s="14"/>
@@ -3441,7 +3575,7 @@
       <c r="Y68" s="14"/>
       <c r="Z68" s="14"/>
     </row>
-    <row r="69" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A69" s="14"/>
       <c r="B69" s="14"/>
       <c r="C69" s="14"/>
@@ -3469,7 +3603,7 @@
       <c r="Y69" s="14"/>
       <c r="Z69" s="14"/>
     </row>
-    <row r="70" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A70" s="14"/>
       <c r="B70" s="14"/>
       <c r="C70" s="14"/>
@@ -3497,7 +3631,7 @@
       <c r="Y70" s="14"/>
       <c r="Z70" s="14"/>
     </row>
-    <row r="71" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A71" s="14"/>
       <c r="B71" s="14"/>
       <c r="C71" s="14"/>
@@ -3525,7 +3659,7 @@
       <c r="Y71" s="14"/>
       <c r="Z71" s="14"/>
     </row>
-    <row r="72" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A72" s="14"/>
       <c r="B72" s="14"/>
       <c r="C72" s="14"/>
@@ -3553,7 +3687,7 @@
       <c r="Y72" s="14"/>
       <c r="Z72" s="14"/>
     </row>
-    <row r="73" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A73" s="14"/>
       <c r="B73" s="14"/>
       <c r="C73" s="14"/>
@@ -3581,7 +3715,7 @@
       <c r="Y73" s="14"/>
       <c r="Z73" s="14"/>
     </row>
-    <row r="74" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A74" s="14"/>
       <c r="B74" s="14"/>
       <c r="C74" s="14"/>
@@ -3609,7 +3743,7 @@
       <c r="Y74" s="14"/>
       <c r="Z74" s="14"/>
     </row>
-    <row r="75" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A75" s="14"/>
       <c r="B75" s="14"/>
       <c r="C75" s="14"/>
@@ -3637,7 +3771,7 @@
       <c r="Y75" s="14"/>
       <c r="Z75" s="14"/>
     </row>
-    <row r="76" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A76" s="14"/>
       <c r="B76" s="14"/>
       <c r="C76" s="14"/>
@@ -3665,7 +3799,7 @@
       <c r="Y76" s="14"/>
       <c r="Z76" s="14"/>
     </row>
-    <row r="77" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A77" s="14"/>
       <c r="B77" s="14"/>
       <c r="C77" s="14"/>
@@ -3693,7 +3827,7 @@
       <c r="Y77" s="14"/>
       <c r="Z77" s="14"/>
     </row>
-    <row r="78" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A78" s="14"/>
       <c r="B78" s="14"/>
       <c r="C78" s="14"/>
@@ -3721,7 +3855,7 @@
       <c r="Y78" s="14"/>
       <c r="Z78" s="14"/>
     </row>
-    <row r="79" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A79" s="14"/>
       <c r="B79" s="14"/>
       <c r="C79" s="14"/>
@@ -3749,7 +3883,7 @@
       <c r="Y79" s="14"/>
       <c r="Z79" s="14"/>
     </row>
-    <row r="80" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A80" s="14"/>
       <c r="B80" s="14"/>
       <c r="C80" s="14"/>
@@ -3777,7 +3911,7 @@
       <c r="Y80" s="14"/>
       <c r="Z80" s="14"/>
     </row>
-    <row r="81" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A81" s="14"/>
       <c r="B81" s="14"/>
       <c r="C81" s="14"/>
@@ -3805,7 +3939,7 @@
       <c r="Y81" s="14"/>
       <c r="Z81" s="14"/>
     </row>
-    <row r="82" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A82" s="14"/>
       <c r="B82" s="14"/>
       <c r="C82" s="14"/>
@@ -3833,7 +3967,7 @@
       <c r="Y82" s="14"/>
       <c r="Z82" s="14"/>
     </row>
-    <row r="83" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A83" s="14"/>
       <c r="B83" s="14"/>
       <c r="C83" s="14"/>
@@ -3861,7 +3995,7 @@
       <c r="Y83" s="14"/>
       <c r="Z83" s="14"/>
     </row>
-    <row r="84" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A84" s="14"/>
       <c r="B84" s="14"/>
       <c r="C84" s="14"/>
@@ -3889,7 +4023,7 @@
       <c r="Y84" s="14"/>
       <c r="Z84" s="14"/>
     </row>
-    <row r="85" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A85" s="14"/>
       <c r="B85" s="14"/>
       <c r="C85" s="14"/>
@@ -3917,7 +4051,7 @@
       <c r="Y85" s="14"/>
       <c r="Z85" s="14"/>
     </row>
-    <row r="86" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A86" s="14"/>
       <c r="B86" s="14"/>
       <c r="C86" s="14"/>
@@ -3945,7 +4079,7 @@
       <c r="Y86" s="14"/>
       <c r="Z86" s="14"/>
     </row>
-    <row r="87" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A87" s="14"/>
       <c r="B87" s="14"/>
       <c r="C87" s="14"/>
@@ -3973,7 +4107,7 @@
       <c r="Y87" s="14"/>
       <c r="Z87" s="14"/>
     </row>
-    <row r="88" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A88" s="14"/>
       <c r="B88" s="14"/>
       <c r="C88" s="14"/>
@@ -4001,7 +4135,7 @@
       <c r="Y88" s="14"/>
       <c r="Z88" s="14"/>
     </row>
-    <row r="89" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A89" s="14"/>
       <c r="B89" s="14"/>
       <c r="C89" s="14"/>
@@ -4029,7 +4163,7 @@
       <c r="Y89" s="14"/>
       <c r="Z89" s="14"/>
     </row>
-    <row r="90" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A90" s="14"/>
       <c r="B90" s="14"/>
       <c r="C90" s="14"/>
@@ -4057,7 +4191,7 @@
       <c r="Y90" s="14"/>
       <c r="Z90" s="14"/>
     </row>
-    <row r="91" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A91" s="14"/>
       <c r="B91" s="14"/>
       <c r="C91" s="14"/>
@@ -4085,7 +4219,7 @@
       <c r="Y91" s="14"/>
       <c r="Z91" s="14"/>
     </row>
-    <row r="92" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A92" s="14"/>
       <c r="B92" s="14"/>
       <c r="C92" s="14"/>
@@ -4113,7 +4247,7 @@
       <c r="Y92" s="14"/>
       <c r="Z92" s="14"/>
     </row>
-    <row r="93" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A93" s="14"/>
       <c r="B93" s="14"/>
       <c r="C93" s="14"/>
@@ -4141,7 +4275,7 @@
       <c r="Y93" s="14"/>
       <c r="Z93" s="14"/>
     </row>
-    <row r="94" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A94" s="14"/>
       <c r="B94" s="14"/>
       <c r="C94" s="14"/>
@@ -4169,7 +4303,7 @@
       <c r="Y94" s="14"/>
       <c r="Z94" s="14"/>
     </row>
-    <row r="95" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A95" s="14"/>
       <c r="B95" s="14"/>
       <c r="C95" s="14"/>
@@ -4197,7 +4331,7 @@
       <c r="Y95" s="14"/>
       <c r="Z95" s="14"/>
     </row>
-    <row r="96" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A96" s="14"/>
       <c r="B96" s="14"/>
       <c r="C96" s="14"/>
@@ -4225,7 +4359,7 @@
       <c r="Y96" s="14"/>
       <c r="Z96" s="14"/>
     </row>
-    <row r="97" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A97" s="14"/>
       <c r="B97" s="14"/>
       <c r="C97" s="14"/>
@@ -4253,7 +4387,7 @@
       <c r="Y97" s="14"/>
       <c r="Z97" s="14"/>
     </row>
-    <row r="98" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A98" s="14"/>
       <c r="B98" s="14"/>
       <c r="C98" s="14"/>
@@ -4281,7 +4415,7 @@
       <c r="Y98" s="14"/>
       <c r="Z98" s="14"/>
     </row>
-    <row r="99" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A99" s="14"/>
       <c r="B99" s="14"/>
       <c r="C99" s="14"/>
@@ -4335,39 +4469,38 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42C030FF-C503-4743-9DBD-437AEB1E949D}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A3:AD37"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.1796875" customWidth="1"/>
-    <col min="2" max="2" width="11.7265625" customWidth="1"/>
-    <col min="3" max="3" width="3.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.54296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.7265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.81640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.453125" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="5.7265625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.1796875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.7265625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.26953125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.7265625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.1796875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="5.7265625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5.54296875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="5.81640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.7265625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="4.81640625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="7.54296875" customWidth="1"/>
-    <col min="25" max="25" width="6.7265625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.28515625" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" customWidth="1"/>
+    <col min="3" max="3" width="3.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7.5703125" customWidth="1"/>
+    <col min="25" max="25" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="27" max="28" width="6" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="5.7265625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="6.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
       <c r="C3" s="6" t="str" cm="1">
         <f t="array" ref="C3">IF(LEFT(INDEX(C5:C7,$A$4),1)&lt;&gt;"*",INDEX(C5:C7,$A$4),"")</f>
         <v>IE</v>
@@ -4481,12 +4614,12 @@
         <v>IE-MN</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>34</v>
       </c>
@@ -4601,7 +4734,7 @@
         <v>IE-MN</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>36</v>
       </c>
@@ -4718,7 +4851,7 @@
         <v>*IE-MN</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>37</v>
       </c>
@@ -4835,7 +4968,7 @@
         <v>IE-MN</v>
       </c>
     </row>
-    <row r="10" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
         <v>38</v>
       </c>
@@ -4843,7 +4976,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
         <v>40</v>
       </c>
@@ -4851,7 +4984,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
         <v>41</v>
       </c>
@@ -4859,7 +4992,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
         <v>42</v>
       </c>
@@ -4867,7 +5000,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
         <v>43</v>
       </c>
@@ -4875,7 +5008,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
         <v>44</v>
       </c>
@@ -4883,7 +5016,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
         <v>45</v>
       </c>
@@ -4891,7 +5024,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>46</v>
       </c>
@@ -4899,7 +5032,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
         <v>47</v>
       </c>
@@ -4907,7 +5040,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>48</v>
       </c>
@@ -4915,7 +5048,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
         <v>49</v>
       </c>
@@ -4923,7 +5056,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>50</v>
       </c>
@@ -4931,7 +5064,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
         <v>51</v>
       </c>
@@ -4939,7 +5072,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>52</v>
       </c>
@@ -4947,7 +5080,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
         <v>53</v>
       </c>
@@ -4955,7 +5088,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>54</v>
       </c>
@@ -4963,7 +5096,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
         <v>55</v>
       </c>
@@ -4971,7 +5104,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>56</v>
       </c>
@@ -4979,7 +5112,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
         <v>57</v>
       </c>
@@ -4987,7 +5120,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>58</v>
       </c>
@@ -4995,7 +5128,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
         <v>59</v>
       </c>
@@ -5003,7 +5136,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>60</v>
       </c>
@@ -5011,7 +5144,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
         <v>61</v>
       </c>
@@ -5019,7 +5152,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>62</v>
       </c>
@@ -5027,7 +5160,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="10" t="s">
         <v>63</v>
       </c>
@@ -5035,7 +5168,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>64</v>
       </c>
@@ -5043,7 +5176,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="10" t="s">
         <v>65</v>
       </c>
@@ -5051,7 +5184,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
         <v>66</v>
       </c>
@@ -5095,44 +5228,43 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AL10"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AM13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.1796875" customWidth="1"/>
+    <col min="2" max="2" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.28515625" customWidth="1"/>
     <col min="6" max="6" width="6" customWidth="1"/>
-    <col min="7" max="7" width="8.26953125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.7265625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.81640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="14" width="5.7265625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.1796875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.81640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="10" max="14" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="6.42578125" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="7" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5.7265625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.7109375" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="6" bestFit="1" customWidth="1"/>
-    <col min="22" max="24" width="5.7265625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="22" max="24" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="6.42578125" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="5" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="6" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="6.26953125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="5.7109375" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="6" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="5.81640625" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="5.7265625" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="6.1796875" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="11.28515625" customWidth="1"/>
+    <col min="36" max="36" width="12.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" ht="21.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:39" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
@@ -5140,7 +5272,7 @@
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
     </row>
-    <row r="3" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:39" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>6</v>
       </c>
@@ -5277,11 +5409,11 @@
       <c r="AK3" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="AL3" s="32" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="4" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="AL3" s="29" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4" spans="1:39" x14ac:dyDescent="0.25">
       <c r="D4" t="s">
         <v>67</v>
       </c>
@@ -5409,11 +5541,11 @@
       <c r="AK4" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="AL4" s="31" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="AL4" s="28" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="5" spans="1:39" x14ac:dyDescent="0.25">
       <c r="D5" t="s">
         <v>67</v>
       </c>
@@ -5541,11 +5673,11 @@
       <c r="AK5" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="AL5" s="31" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="AL5" s="28" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="6" spans="1:39" x14ac:dyDescent="0.25">
       <c r="D6" t="s">
         <v>67</v>
       </c>
@@ -5673,11 +5805,11 @@
       <c r="AK6" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="AL6" s="31" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="AL6" s="28" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="7" spans="1:39" x14ac:dyDescent="0.25">
       <c r="D7" t="s">
         <v>67</v>
       </c>
@@ -5805,11 +5937,11 @@
       <c r="AK7" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="AL7" s="31" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="AL7" s="28" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="8" spans="1:39" x14ac:dyDescent="0.25">
       <c r="D8" t="s">
         <v>67</v>
       </c>
@@ -5937,268 +6069,414 @@
       <c r="AK8" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="AL8" s="31" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.35">
-      <c r="D9" s="33" t="s">
+      <c r="AL8" s="28" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="9" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="D9" t="s">
         <v>67</v>
       </c>
-      <c r="F9" s="33">
+      <c r="F9">
         <v>74.099999999999994</v>
       </c>
-      <c r="G9" s="33">
+      <c r="G9">
         <f t="shared" si="1"/>
         <v>74.099999999999994</v>
       </c>
-      <c r="H9" s="33">
+      <c r="H9">
         <f t="shared" si="1"/>
         <v>74.099999999999994</v>
       </c>
-      <c r="I9" s="33">
+      <c r="I9">
         <f t="shared" si="1"/>
         <v>74.099999999999994</v>
       </c>
-      <c r="J9" s="33">
+      <c r="J9">
         <f t="shared" si="1"/>
         <v>74.099999999999994</v>
       </c>
-      <c r="K9" s="33">
+      <c r="K9">
         <f t="shared" si="1"/>
         <v>74.099999999999994</v>
       </c>
-      <c r="L9" s="33">
+      <c r="L9">
         <f t="shared" si="1"/>
         <v>74.099999999999994</v>
       </c>
-      <c r="M9" s="33">
+      <c r="M9">
         <f t="shared" si="1"/>
         <v>74.099999999999994</v>
       </c>
-      <c r="N9" s="33">
+      <c r="N9">
         <f t="shared" si="1"/>
         <v>74.099999999999994</v>
       </c>
-      <c r="O9" s="33">
+      <c r="O9">
         <f t="shared" si="1"/>
         <v>74.099999999999994</v>
       </c>
-      <c r="P9" s="33">
+      <c r="P9">
         <f t="shared" si="1"/>
         <v>74.099999999999994</v>
       </c>
-      <c r="Q9" s="33">
+      <c r="Q9">
         <f t="shared" si="1"/>
         <v>74.099999999999994</v>
       </c>
-      <c r="R9" s="33">
+      <c r="R9">
         <f t="shared" si="1"/>
         <v>74.099999999999994</v>
       </c>
-      <c r="S9" s="33">
+      <c r="S9">
         <f t="shared" si="1"/>
         <v>74.099999999999994</v>
       </c>
-      <c r="T9" s="33">
+      <c r="T9">
         <f t="shared" si="1"/>
         <v>74.099999999999994</v>
       </c>
-      <c r="U9" s="33">
+      <c r="U9">
         <f t="shared" si="1"/>
         <v>74.099999999999994</v>
       </c>
-      <c r="V9" s="33">
+      <c r="V9">
         <f t="shared" si="1"/>
         <v>74.099999999999994</v>
       </c>
-      <c r="W9" s="33">
+      <c r="W9">
         <f t="shared" si="0"/>
         <v>74.099999999999994</v>
       </c>
-      <c r="X9" s="33">
+      <c r="X9">
         <f t="shared" si="0"/>
         <v>74.099999999999994</v>
       </c>
-      <c r="Y9" s="33">
+      <c r="Y9">
         <f t="shared" si="0"/>
         <v>74.099999999999994</v>
       </c>
-      <c r="Z9" s="33">
+      <c r="Z9">
         <f t="shared" si="0"/>
         <v>74.099999999999994</v>
       </c>
-      <c r="AA9" s="33">
+      <c r="AA9">
         <f t="shared" si="0"/>
         <v>74.099999999999994</v>
       </c>
-      <c r="AB9" s="33">
+      <c r="AB9">
         <f t="shared" si="0"/>
         <v>74.099999999999994</v>
       </c>
-      <c r="AC9" s="33">
+      <c r="AC9">
         <f t="shared" si="0"/>
         <v>74.099999999999994</v>
       </c>
-      <c r="AD9" s="33">
+      <c r="AD9">
         <f t="shared" si="0"/>
         <v>74.099999999999994</v>
       </c>
-      <c r="AE9" s="33">
+      <c r="AE9">
         <f t="shared" si="0"/>
         <v>74.099999999999994</v>
       </c>
-      <c r="AF9" s="33">
+      <c r="AF9">
         <f t="shared" si="0"/>
         <v>74.099999999999994</v>
       </c>
-      <c r="AG9" s="33">
+      <c r="AG9">
         <f t="shared" si="0"/>
         <v>74.099999999999994</v>
       </c>
       <c r="AH9" t="s">
         <v>72</v>
       </c>
-      <c r="AI9" s="33" t="s">
-        <v>98</v>
-      </c>
-      <c r="AJ9" s="33" t="s">
+      <c r="AI9" t="s">
+        <v>96</v>
+      </c>
+      <c r="AJ9" t="s">
         <v>72</v>
       </c>
-      <c r="AL9" s="33" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.35">
-      <c r="D10" s="33" t="s">
+      <c r="AK9" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="AL9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="10" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="D10" t="s">
         <v>67</v>
       </c>
-      <c r="F10" s="33">
+      <c r="F10">
         <v>71.900000000000006</v>
       </c>
-      <c r="G10" s="33">
+      <c r="G10">
         <f t="shared" si="1"/>
         <v>71.900000000000006</v>
       </c>
-      <c r="H10" s="33">
+      <c r="H10">
         <f t="shared" si="0"/>
         <v>71.900000000000006</v>
       </c>
-      <c r="I10" s="33">
+      <c r="I10">
         <f t="shared" si="0"/>
         <v>71.900000000000006</v>
       </c>
-      <c r="J10" s="33">
+      <c r="J10">
         <f t="shared" si="0"/>
         <v>71.900000000000006</v>
       </c>
-      <c r="K10" s="33">
+      <c r="K10">
         <f t="shared" si="0"/>
         <v>71.900000000000006</v>
       </c>
-      <c r="L10" s="33">
+      <c r="L10">
         <f t="shared" si="0"/>
         <v>71.900000000000006</v>
       </c>
-      <c r="M10" s="33">
+      <c r="M10">
         <f t="shared" si="0"/>
         <v>71.900000000000006</v>
       </c>
-      <c r="N10" s="33">
+      <c r="N10">
         <f t="shared" si="0"/>
         <v>71.900000000000006</v>
       </c>
-      <c r="O10" s="33">
+      <c r="O10">
         <f t="shared" si="0"/>
         <v>71.900000000000006</v>
       </c>
-      <c r="P10" s="33">
+      <c r="P10">
         <f t="shared" si="0"/>
         <v>71.900000000000006</v>
       </c>
-      <c r="Q10" s="33">
+      <c r="Q10">
         <f t="shared" si="0"/>
         <v>71.900000000000006</v>
       </c>
-      <c r="R10" s="33">
+      <c r="R10">
         <f t="shared" si="0"/>
         <v>71.900000000000006</v>
       </c>
-      <c r="S10" s="33">
+      <c r="S10">
         <f t="shared" si="0"/>
         <v>71.900000000000006</v>
       </c>
-      <c r="T10" s="33">
+      <c r="T10">
         <f t="shared" si="0"/>
         <v>71.900000000000006</v>
       </c>
-      <c r="U10" s="33">
+      <c r="U10">
         <f t="shared" si="0"/>
         <v>71.900000000000006</v>
       </c>
-      <c r="V10" s="33">
+      <c r="V10">
         <f t="shared" si="0"/>
         <v>71.900000000000006</v>
       </c>
-      <c r="W10" s="33">
+      <c r="W10">
         <f t="shared" si="0"/>
         <v>71.900000000000006</v>
       </c>
-      <c r="X10" s="33">
+      <c r="X10">
         <f t="shared" si="0"/>
         <v>71.900000000000006</v>
       </c>
-      <c r="Y10" s="33">
+      <c r="Y10">
         <f t="shared" si="0"/>
         <v>71.900000000000006</v>
       </c>
-      <c r="Z10" s="33">
+      <c r="Z10">
         <f t="shared" si="0"/>
         <v>71.900000000000006</v>
       </c>
-      <c r="AA10" s="33">
+      <c r="AA10">
         <f t="shared" si="0"/>
         <v>71.900000000000006</v>
       </c>
-      <c r="AB10" s="33">
+      <c r="AB10">
         <f t="shared" si="0"/>
         <v>71.900000000000006</v>
       </c>
-      <c r="AC10" s="33">
+      <c r="AC10">
         <f t="shared" si="0"/>
         <v>71.900000000000006</v>
       </c>
-      <c r="AD10" s="33">
+      <c r="AD10">
         <f t="shared" si="0"/>
         <v>71.900000000000006</v>
       </c>
-      <c r="AE10" s="33">
+      <c r="AE10">
         <f t="shared" si="0"/>
         <v>71.900000000000006</v>
       </c>
-      <c r="AF10" s="33">
+      <c r="AF10">
         <f t="shared" si="0"/>
         <v>71.900000000000006</v>
       </c>
-      <c r="AG10" s="33">
+      <c r="AG10">
         <f t="shared" si="0"/>
         <v>71.900000000000006</v>
       </c>
       <c r="AH10" t="s">
         <v>75</v>
       </c>
-      <c r="AI10" s="33" t="s">
-        <v>98</v>
-      </c>
-      <c r="AJ10" s="33" t="s">
+      <c r="AI10" t="s">
+        <v>96</v>
+      </c>
+      <c r="AJ10" t="s">
         <v>75</v>
       </c>
-      <c r="AL10" s="33" t="s">
-        <v>95</v>
+      <c r="AK10" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="AL10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="11" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="D11" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30">
+        <f>(7.4+11.6)/2</f>
+        <v>9.5</v>
+      </c>
+      <c r="G11" s="30">
+        <f t="shared" ref="G11:AG11" si="3">(7.4+11.6)/2</f>
+        <v>9.5</v>
+      </c>
+      <c r="H11" s="30">
+        <f t="shared" si="3"/>
+        <v>9.5</v>
+      </c>
+      <c r="I11" s="30">
+        <f t="shared" si="3"/>
+        <v>9.5</v>
+      </c>
+      <c r="J11" s="30">
+        <f t="shared" si="3"/>
+        <v>9.5</v>
+      </c>
+      <c r="K11" s="30">
+        <f t="shared" si="3"/>
+        <v>9.5</v>
+      </c>
+      <c r="L11" s="30">
+        <f t="shared" si="3"/>
+        <v>9.5</v>
+      </c>
+      <c r="M11" s="30">
+        <f t="shared" si="3"/>
+        <v>9.5</v>
+      </c>
+      <c r="N11" s="30">
+        <f t="shared" si="3"/>
+        <v>9.5</v>
+      </c>
+      <c r="O11" s="30">
+        <f t="shared" si="3"/>
+        <v>9.5</v>
+      </c>
+      <c r="P11" s="30">
+        <f t="shared" si="3"/>
+        <v>9.5</v>
+      </c>
+      <c r="Q11" s="30">
+        <f t="shared" si="3"/>
+        <v>9.5</v>
+      </c>
+      <c r="R11" s="30">
+        <f t="shared" si="3"/>
+        <v>9.5</v>
+      </c>
+      <c r="S11" s="30">
+        <f t="shared" si="3"/>
+        <v>9.5</v>
+      </c>
+      <c r="T11" s="30">
+        <f t="shared" si="3"/>
+        <v>9.5</v>
+      </c>
+      <c r="U11" s="30">
+        <f t="shared" si="3"/>
+        <v>9.5</v>
+      </c>
+      <c r="V11" s="30">
+        <f t="shared" si="3"/>
+        <v>9.5</v>
+      </c>
+      <c r="W11" s="30">
+        <f t="shared" si="3"/>
+        <v>9.5</v>
+      </c>
+      <c r="X11" s="30">
+        <f t="shared" si="3"/>
+        <v>9.5</v>
+      </c>
+      <c r="Y11" s="30">
+        <f t="shared" si="3"/>
+        <v>9.5</v>
+      </c>
+      <c r="Z11" s="30">
+        <f t="shared" si="3"/>
+        <v>9.5</v>
+      </c>
+      <c r="AA11" s="30">
+        <f t="shared" si="3"/>
+        <v>9.5</v>
+      </c>
+      <c r="AB11" s="30">
+        <f t="shared" si="3"/>
+        <v>9.5</v>
+      </c>
+      <c r="AC11" s="30">
+        <f t="shared" si="3"/>
+        <v>9.5</v>
+      </c>
+      <c r="AD11" s="30">
+        <f t="shared" si="3"/>
+        <v>9.5</v>
+      </c>
+      <c r="AE11" s="30">
+        <f t="shared" si="3"/>
+        <v>9.5</v>
+      </c>
+      <c r="AF11" s="30">
+        <f t="shared" si="3"/>
+        <v>9.5</v>
+      </c>
+      <c r="AG11" s="30">
+        <f t="shared" si="3"/>
+        <v>9.5</v>
+      </c>
+      <c r="AH11" s="30" t="s">
+        <v>100</v>
+      </c>
+      <c r="AI11" s="30" t="s">
+        <v>76</v>
+      </c>
+      <c r="AJ11" s="30" t="s">
+        <v>100</v>
+      </c>
+      <c r="AK11" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="AL11" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="AM11" s="30"/>
+    </row>
+    <row r="13" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="E13" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>